--- a/cronograma.xlsx
+++ b/cronograma.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,32 +478,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Migración Cloud Core</t>
+          <t>App E-Learning v5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TechCorp S.A.</t>
+          <t>FinTech Innova</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>150000</v>
+        <v>170000</v>
       </c>
       <c r="E2" t="n">
-        <v>320</v>
+        <v>559</v>
       </c>
       <c r="F2" t="n">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46037</v>
+        <v>46156</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46203</v>
+        <v>46216</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>N2</t>
         </is>
       </c>
     </row>
@@ -515,28 +515,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>App Móvil B2B</t>
+          <t>E-commerce IA v4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Global Trade</t>
+          <t>AgroSmart</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>85000</v>
+        <v>200000</v>
       </c>
       <c r="E3" t="n">
-        <v>200</v>
+        <v>259</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>46042</v>
+        <v>46144</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -552,28 +552,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sistema de Ciberseguridad</t>
+          <t>Automatización RPA v1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Banco Central</t>
+          <t>AgroSmart</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>340000</v>
+        <v>250000</v>
       </c>
       <c r="E4" t="n">
-        <v>600</v>
+        <v>718</v>
       </c>
       <c r="F4" t="n">
-        <v>110</v>
+        <v>43</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46058</v>
+        <v>46150</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46356</v>
+        <v>46170</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -589,32 +589,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Auditoría de Sistemas</t>
+          <t>Modernización Data Center v1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HealthPlus</t>
+          <t>FinTech Innova</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>45000</v>
+        <v>80000</v>
       </c>
       <c r="E5" t="n">
-        <v>120</v>
+        <v>665</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46071</v>
+        <v>46190</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>46122</v>
+        <v>46234</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>N3</t>
         </is>
       </c>
     </row>
@@ -626,28 +626,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ERP Integración</t>
+          <t>Portal del Ciudadano v2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Motores del Sur</t>
+          <t>RetailPro</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>210000</v>
+        <v>70000</v>
       </c>
       <c r="E6" t="n">
-        <v>450</v>
+        <v>146</v>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46082</v>
+        <v>46183</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>46280</v>
+        <v>46221</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -663,32 +663,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Portal del Empleado</t>
+          <t>App Móvil B2B v2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Retail Group</t>
+          <t>Global Trade</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>65000</v>
+        <v>270000</v>
       </c>
       <c r="E7" t="n">
-        <v>180</v>
+        <v>384</v>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>68</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46091</v>
+        <v>46193</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>46193</v>
+        <v>46226</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>N3</t>
         </is>
       </c>
     </row>
@@ -700,32 +700,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Automatización RPA</t>
+          <t>Plataforma Nacional IoT v3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FinTech Innova</t>
+          <t>HealthPlus</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>125000</v>
+        <v>450000</v>
       </c>
       <c r="E8" t="n">
-        <v>280</v>
+        <v>373</v>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46103</v>
+        <v>46167</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>46235</v>
+        <v>46192</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>N3</t>
         </is>
       </c>
     </row>
@@ -737,32 +737,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mantenimiento Servidores</t>
+          <t>Portal del Ciudadano v2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EduNet</t>
+          <t>Ministerio Defensa</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>35000</v>
+        <v>490000</v>
       </c>
       <c r="E9" t="n">
-        <v>90</v>
+        <v>350</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46117</v>
+        <v>46185</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>46387</v>
+        <v>46204</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N2</t>
         </is>
       </c>
     </row>
@@ -774,28 +774,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Plataforma IoT</t>
+          <t>Soporte Nivel 3 v5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AgroSmart</t>
+          <t>HealthPlus</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>275000</v>
+        <v>460000</v>
       </c>
       <c r="E10" t="n">
-        <v>520</v>
+        <v>432</v>
       </c>
       <c r="F10" t="n">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46127</v>
+        <v>46168</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>46325</v>
+        <v>46200</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -811,32 +811,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Renovación Redes</t>
+          <t>Automatización RPA v3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>City Council</t>
+          <t>Global Trade</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>190000</v>
+        <v>160000</v>
       </c>
       <c r="E11" t="n">
-        <v>350</v>
+        <v>680</v>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>46144</v>
+        <v>46146</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>46266</v>
+        <v>46181</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N1</t>
         </is>
       </c>
     </row>
@@ -848,28 +848,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CRM Personalizado</t>
+          <t>Automatización RPA v4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AutoVentas</t>
+          <t>Banco Central</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>95000</v>
+        <v>190000</v>
       </c>
       <c r="E12" t="n">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46154</v>
+        <v>46185</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46249</v>
+        <v>46231</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -885,32 +885,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Migración a Office 365</t>
+          <t>ERP Integración v5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LawFirm Asoc.</t>
+          <t>FinTech Innova</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>28000</v>
+        <v>400000</v>
       </c>
       <c r="E13" t="n">
-        <v>80</v>
+        <v>508</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46162</v>
+        <v>46179</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>46203</v>
+        <v>46228</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>N1</t>
         </is>
       </c>
     </row>
@@ -922,28 +922,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Data Warehouse</t>
+          <t>Blockchain Trazabilidad v1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PharmaTech</t>
+          <t>Logistica XXI</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>410000</v>
+        <v>60000</v>
       </c>
       <c r="E14" t="n">
-        <v>750</v>
+        <v>212</v>
       </c>
       <c r="F14" t="n">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>46174</v>
+        <v>46152</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>46446</v>
+        <v>46199</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -959,28 +959,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>App de Logística</t>
+          <t>Automatización RPA v5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TransPort SL</t>
+          <t>Global Trade</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>155000</v>
+        <v>270000</v>
       </c>
       <c r="E15" t="n">
-        <v>310</v>
+        <v>490</v>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46181</v>
+        <v>46154</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46341</v>
+        <v>46212</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -996,28 +996,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IA para Atención al Cliente</t>
+          <t>Modernización Data Center v1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TelcoNet</t>
+          <t>EducaTech</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>290000</v>
+        <v>490000</v>
       </c>
       <c r="E16" t="n">
-        <v>480</v>
+        <v>217</v>
       </c>
       <c r="F16" t="n">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46188</v>
+        <v>46177</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>46376</v>
+        <v>46208</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1033,28 +1033,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>E-commerce B2C</t>
+          <t>Sistema Gestión Flotas v3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Moda Rápida</t>
+          <t>Global Trade</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>110000</v>
+        <v>210000</v>
       </c>
       <c r="E17" t="n">
-        <v>240</v>
+        <v>545</v>
       </c>
       <c r="F17" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46204</v>
+        <v>46192</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>46310</v>
+        <v>46224</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1070,32 +1070,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sistema de Reservas</t>
+          <t>Modernización Data Center v2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hoteles Mar</t>
+          <t>Ministerio Defensa</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>75000</v>
+        <v>90000</v>
       </c>
       <c r="E18" t="n">
-        <v>190</v>
+        <v>740</v>
       </c>
       <c r="F18" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46213</v>
+        <v>46144</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46295</v>
+        <v>46175</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>N3</t>
         </is>
       </c>
     </row>
@@ -1107,32 +1107,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Virtualización de Escritorios</t>
+          <t>Auditoría de Sistemas v2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seguros Vida</t>
+          <t>AgroSmart</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>135000</v>
+        <v>130000</v>
       </c>
       <c r="E19" t="n">
-        <v>260</v>
+        <v>652</v>
       </c>
       <c r="F19" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46225</v>
+        <v>46176</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>46327</v>
+        <v>46229</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N1</t>
         </is>
       </c>
     </row>
@@ -1144,28 +1144,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Intranet Corporativa</t>
+          <t>Blockchain Trazabilidad v1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FoodCorp</t>
+          <t>Global Trade</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>55000</v>
+        <v>260000</v>
       </c>
       <c r="E20" t="n">
-        <v>150</v>
+        <v>414</v>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46239</v>
+        <v>46182</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>46325</v>
+        <v>46217</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1181,30 +1181,400 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Blockchain Trazabilidad</t>
+          <t>App Móvil B2B v1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>RetailPro</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>340000</v>
+      </c>
+      <c r="E21" t="n">
+        <v>170</v>
+      </c>
+      <c r="F21" t="n">
+        <v>78</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>46159</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LIC-2026-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Blockchain Trazabilidad v5</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Banco Central</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>190000</v>
+      </c>
+      <c r="E22" t="n">
+        <v>640</v>
+      </c>
+      <c r="F22" t="n">
+        <v>87</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LIC-2026-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sistema Gestión Flotas v2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>RetailPro</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>220000</v>
+      </c>
+      <c r="E23" t="n">
+        <v>508</v>
+      </c>
+      <c r="F23" t="n">
+        <v>95</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LIC-2026-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Soporte Nivel 3 v5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>Exportadores SL</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>380000</v>
-      </c>
-      <c r="E21" t="n">
-        <v>620</v>
-      </c>
-      <c r="F21" t="n">
-        <v>95</v>
-      </c>
-      <c r="G21" s="1" t="n">
-        <v>46249</v>
-      </c>
-      <c r="H21" s="1" t="n">
-        <v>46418</v>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="D24" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E24" t="n">
+        <v>353</v>
+      </c>
+      <c r="F24" t="n">
+        <v>38</v>
+      </c>
+      <c r="G24" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LIC-2026-024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Portal del Ciudadano v5</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>HealthPlus</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>400000</v>
+      </c>
+      <c r="E25" t="n">
+        <v>325</v>
+      </c>
+      <c r="F25" t="n">
+        <v>10</v>
+      </c>
+      <c r="G25" s="1" t="n">
+        <v>46165</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LIC-2026-025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Migración Cloud Core v2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Global Trade</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E26" t="n">
+        <v>438</v>
+      </c>
+      <c r="F26" t="n">
+        <v>19</v>
+      </c>
+      <c r="G26" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LIC-2026-026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>App E-Learning v4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>HealthPlus</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>370000</v>
+      </c>
+      <c r="E27" t="n">
+        <v>235</v>
+      </c>
+      <c r="F27" t="n">
+        <v>83</v>
+      </c>
+      <c r="G27" s="1" t="n">
+        <v>46159</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LIC-2026-027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sistema Gestión Flotas v4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Logistica XXI</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>290000</v>
+      </c>
+      <c r="E28" t="n">
+        <v>294</v>
+      </c>
+      <c r="F28" t="n">
+        <v>22</v>
+      </c>
+      <c r="G28" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LIC-2026-028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Plataforma Nacional IoT v4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>FinTech Innova</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>320000</v>
+      </c>
+      <c r="E29" t="n">
+        <v>155</v>
+      </c>
+      <c r="F29" t="n">
+        <v>96</v>
+      </c>
+      <c r="G29" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LIC-2026-029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Migración Cloud Core v4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>RetailPro</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>240000</v>
+      </c>
+      <c r="E30" t="n">
+        <v>211</v>
+      </c>
+      <c r="F30" t="n">
+        <v>41</v>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>LIC-2026-030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Blockchain Trazabilidad v2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>FinTech Innova</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>140000</v>
+      </c>
+      <c r="E31" t="n">
+        <v>385</v>
+      </c>
+      <c r="F31" t="n">
+        <v>69</v>
+      </c>
+      <c r="G31" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>N1</t>
         </is>
@@ -1221,7 +1591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1299,22 +1669,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Beatriz Gómez</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
           <t>Carlos Vega</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Elena Navarro</t>
+          <t>Tomás Fuentes</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Migración Cloud Core</t>
+          <t>App E-Learning v5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1324,76 +1690,72 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>TechCorp S.A.</t>
+          <t>FinTech Innova</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>150000</v>
+        <v>170000</v>
       </c>
       <c r="I2" t="n">
-        <v>320</v>
+        <v>559</v>
       </c>
       <c r="J2" t="n">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>46037</v>
+        <v>46156</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46203</v>
+        <v>46216</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>N2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LIC-2026-012</t>
+          <t>LIC-2026-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diana Torres</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Natalia Ortiz</t>
-        </is>
-      </c>
+          <t>Ana Martínez</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Migración a Office 365</t>
+          <t>E-commerce IA v4</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>En estudio</t>
+          <t>Estudio previo</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>LawFirm Asoc.</t>
+          <t>AgroSmart</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>28000</v>
+        <v>200000</v>
       </c>
       <c r="I3" t="n">
-        <v>80</v>
+        <v>259</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>46162</v>
+        <v>46144</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46203</v>
+        <v>46169</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1404,23 +1766,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LIC-2026-020</t>
+          <t>LIC-2026-003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Natalia Ortiz</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>Beatriz Gómez</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Diana Torres</t>
+          <t>Fernando Gil</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Blockchain Trazabilidad</t>
+          <t>Automatización RPA v1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1430,23 +1796,23 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Exportadores SL</t>
+          <t>AgroSmart</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>380000</v>
+        <v>250000</v>
       </c>
       <c r="I4" t="n">
-        <v>620</v>
+        <v>718</v>
       </c>
       <c r="J4" t="n">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>46249</v>
+        <v>46150</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46418</v>
+        <v>46170</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1457,113 +1823,129 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LIC-2026-003</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>LIC-2026-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Patricia Rojas</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Patricia Rojas</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Javier Ramos</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Oscar Díaz</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sistema de Ciberseguridad</t>
+          <t>Modernización Data Center v1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>En estudio</t>
+          <t>Estudio previo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Banco Central</t>
+          <t>FinTech Innova</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>340000</v>
+        <v>80000</v>
       </c>
       <c r="I5" t="n">
-        <v>600</v>
+        <v>665</v>
       </c>
       <c r="J5" t="n">
-        <v>110</v>
+        <v>47</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>46058</v>
+        <v>46190</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>46356</v>
+        <v>46234</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>N3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LIC-2026-002</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>LIC-2026-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Raúl Mendoza</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Gabriel Silva</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>App Móvil B2B</t>
+          <t>Portal del Ciudadano v2</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pendiente Asignar</t>
+          <t>En estudio</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Global Trade</t>
+          <t>RetailPro</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>85000</v>
+        <v>70000</v>
       </c>
       <c r="I6" t="n">
-        <v>200</v>
+        <v>146</v>
       </c>
       <c r="J6" t="n">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>46042</v>
+        <v>46183</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46157</v>
+        <v>46221</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>N1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LIC-2026-005</t>
+          <t>LIC-2026-006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hugo Marín</t>
+          <t>Tomás Fuentes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ERP Integración</t>
+          <t>App Móvil B2B v2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1573,76 +1955,1234 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Motores del Sur</t>
+          <t>Global Trade</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>210000</v>
+        <v>270000</v>
       </c>
       <c r="I7" t="n">
-        <v>450</v>
+        <v>384</v>
       </c>
       <c r="J7" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46082</v>
+        <v>46193</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46280</v>
+        <v>46226</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>N1</t>
+          <t>N3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LIC-2026-018</t>
+          <t>LIC-2026-007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Oscar Prieto</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>Sofía Vargas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Fernando Gil</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Virtualización de Escritorios</t>
+          <t>Plataforma Nacional IoT v3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>En estudio</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HealthPlus</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>450000</v>
+      </c>
+      <c r="I8" t="n">
+        <v>373</v>
+      </c>
+      <c r="J8" t="n">
+        <v>99</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LIC-2026-008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Portal del Ciudadano v2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pendiente Asignar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ministerio Defensa</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>490000</v>
+      </c>
+      <c r="I9" t="n">
+        <v>350</v>
+      </c>
+      <c r="J9" t="n">
+        <v>30</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LIC-2026-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Hugo Morales</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Úrsula Perea</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Soporte Nivel 3 v5</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>En estudio</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HealthPlus</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>460000</v>
+      </c>
+      <c r="I10" t="n">
+        <v>432</v>
+      </c>
+      <c r="J10" t="n">
+        <v>17</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LIC-2026-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Úrsula Perea</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sofía Vargas</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Automatización RPA v3</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>En estudio</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Global Trade</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>160000</v>
+      </c>
+      <c r="I11" t="n">
+        <v>680</v>
+      </c>
+      <c r="J11" t="n">
+        <v>50</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LIC-2026-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hugo Morales</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Natalia Ortiz</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Automatización RPA v4</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>En estudio</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Banco Central</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>190000</v>
+      </c>
+      <c r="I12" t="n">
+        <v>242</v>
+      </c>
+      <c r="J12" t="n">
+        <v>41</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LIC-2026-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Laura Jiménez</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Carlos Vega</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ana Martínez</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ERP Integración v5</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>En estudio</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FinTech Innova</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I13" t="n">
+        <v>508</v>
+      </c>
+      <c r="J13" t="n">
+        <v>56</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LIC-2026-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Carlos Vega</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Tomás Fuentes</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Blockchain Trazabilidad v1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>En estudio</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Logistica XXI</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I14" t="n">
+        <v>212</v>
+      </c>
+      <c r="J14" t="n">
+        <v>29</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LIC-2026-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Automatización RPA v5</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pendiente Asignar</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Global Trade</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>270000</v>
+      </c>
+      <c r="I15" t="n">
+        <v>490</v>
+      </c>
+      <c r="J15" t="n">
+        <v>86</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LIC-2026-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Javier Ramos</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Sofía Vargas</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Modernización Data Center v1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>En estudio</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>EducaTech</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>490000</v>
+      </c>
+      <c r="I16" t="n">
+        <v>217</v>
+      </c>
+      <c r="J16" t="n">
+        <v>97</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LIC-2026-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Elena Navarro</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Isabel Castro</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Diana Torres</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sistema Gestión Flotas v3</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>En estudio</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Global Trade</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>210000</v>
+      </c>
+      <c r="I17" t="n">
+        <v>545</v>
+      </c>
+      <c r="J17" t="n">
+        <v>30</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LIC-2026-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Isabel Castro</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Javier Ramos</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Modernización Data Center v2</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>En estudio</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ministerio Defensa</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>90000</v>
+      </c>
+      <c r="I18" t="n">
+        <v>740</v>
+      </c>
+      <c r="J18" t="n">
+        <v>48</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>46144</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LIC-2026-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sofía Vargas</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Raúl Mendoza</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Isabel Castro</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Auditoría de Sistemas v2</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>Estudio previo</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Seguros Vida</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>135000</v>
-      </c>
-      <c r="I8" t="n">
-        <v>260</v>
-      </c>
-      <c r="J8" t="n">
-        <v>30</v>
-      </c>
-      <c r="K8" s="1" t="n">
-        <v>46225</v>
-      </c>
-      <c r="L8" s="1" t="n">
-        <v>46327</v>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>AgroSmart</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>130000</v>
+      </c>
+      <c r="I19" t="n">
+        <v>652</v>
+      </c>
+      <c r="J19" t="n">
+        <v>77</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LIC-2026-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Oscar Díaz</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Beatriz Gómez</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Blockchain Trazabilidad v1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>En estudio</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Global Trade</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>260000</v>
+      </c>
+      <c r="I20" t="n">
+        <v>414</v>
+      </c>
+      <c r="J20" t="n">
+        <v>40</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="L20" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LIC-2026-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Fernando Gil</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Patricia Rojas</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>App Móvil B2B v1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>En estudio</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>RetailPro</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>340000</v>
+      </c>
+      <c r="I21" t="n">
+        <v>170</v>
+      </c>
+      <c r="J21" t="n">
+        <v>78</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>46159</v>
+      </c>
+      <c r="L21" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LIC-2026-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Blockchain Trazabilidad v5</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Pendiente Asignar</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Banco Central</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>190000</v>
+      </c>
+      <c r="I22" t="n">
+        <v>640</v>
+      </c>
+      <c r="J22" t="n">
+        <v>87</v>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>46152</v>
+      </c>
+      <c r="L22" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LIC-2026-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Elena Navarro</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sistema Gestión Flotas v2</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>En estudio</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>RetailPro</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>220000</v>
+      </c>
+      <c r="I23" t="n">
+        <v>508</v>
+      </c>
+      <c r="J23" t="n">
+        <v>95</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="L23" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>N3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LIC-2026-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Marcos López</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Gabriel Silva</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Soporte Nivel 3 v5</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Estudio previo</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Exportadores SL</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I24" t="n">
+        <v>353</v>
+      </c>
+      <c r="J24" t="n">
+        <v>38</v>
+      </c>
+      <c r="K24" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="L24" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LIC-2026-024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Oscar Díaz</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Elena Navarro</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Hugo Morales</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Portal del Ciudadano v5</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>En estudio</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>HealthPlus</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I25" t="n">
+        <v>325</v>
+      </c>
+      <c r="J25" t="n">
+        <v>10</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <v>46165</v>
+      </c>
+      <c r="L25" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LIC-2026-025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Oscar Díaz</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ana Martínez</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Migración Cloud Core v2</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>En estudio</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Global Trade</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>50000</v>
+      </c>
+      <c r="I26" t="n">
+        <v>438</v>
+      </c>
+      <c r="J26" t="n">
+        <v>19</v>
+      </c>
+      <c r="K26" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="L26" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LIC-2026-026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Hugo Morales</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Isabel Castro</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>App E-Learning v4</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>En estudio</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>HealthPlus</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>370000</v>
+      </c>
+      <c r="I27" t="n">
+        <v>235</v>
+      </c>
+      <c r="J27" t="n">
+        <v>83</v>
+      </c>
+      <c r="K27" s="1" t="n">
+        <v>46159</v>
+      </c>
+      <c r="L27" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LIC-2026-027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Raúl Mendoza</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Hugo Morales</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sistema Gestión Flotas v4</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Estudio previo</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Logistica XXI</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>290000</v>
+      </c>
+      <c r="I28" t="n">
+        <v>294</v>
+      </c>
+      <c r="J28" t="n">
+        <v>22</v>
+      </c>
+      <c r="K28" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="L28" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>N1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LIC-2026-028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Hugo Morales</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Víctor Reyes</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Plataforma Nacional IoT v4</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>En estudio</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>FinTech Innova</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>320000</v>
+      </c>
+      <c r="I29" t="n">
+        <v>155</v>
+      </c>
+      <c r="J29" t="n">
+        <v>96</v>
+      </c>
+      <c r="K29" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="L29" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LIC-2026-029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Carlos Vega</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Isabel Castro</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Migración Cloud Core v4</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>En estudio</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>RetailPro</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>240000</v>
+      </c>
+      <c r="I30" t="n">
+        <v>211</v>
+      </c>
+      <c r="J30" t="n">
+        <v>41</v>
+      </c>
+      <c r="K30" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="L30" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>N1</t>
         </is>
       </c>
     </row>
@@ -1657,7 +3197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1685,12 +3225,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TEC-02</t>
+          <t>TEC-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Beatriz Gómez</t>
+          <t>Ana Martínez</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1705,17 +3245,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TEC-03</t>
+          <t>TEC-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Carlos Vega</t>
+          <t>Beatriz Gómez</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Arquitecto de Software</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -1725,17 +3265,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TEC-04</t>
+          <t>TEC-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Diana Torres</t>
+          <t>Carlos Vega</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1745,17 +3285,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TEC-05</t>
+          <t>TEC-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Elena Navarro</t>
+          <t>Diana Torres</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1765,17 +3305,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TEC-06</t>
+          <t>TEC-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fernando Gil</t>
+          <t>Elena Navarro</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>QA Automation</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1785,17 +3325,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TEC-07</t>
+          <t>TEC-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gabriel Sanz</t>
+          <t>Fernando Gil</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Scrum Master</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1805,17 +3345,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TEC-08</t>
+          <t>TEC-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hugo Marín</t>
+          <t>Gabriel Silva</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UX/UI Designer</t>
+          <t>Frontend Developer</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1825,17 +3365,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TEC-09</t>
+          <t>TEC-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Isabel Castro</t>
+          <t>Hugo Morales</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Product Owner</t>
+          <t>SysAdmin</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1845,17 +3385,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TEC-10</t>
+          <t>TEC-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Javier Blanco</t>
+          <t>Isabel Castro</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Frontend Developer</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1865,17 +3405,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TEC-11</t>
+          <t>TEC-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Laura Molina</t>
+          <t>Javier Ramos</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Frontend Developer</t>
+          <t>Product Owner</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1885,17 +3425,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TEC-12</t>
+          <t>TEC-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mario Delgado</t>
+          <t>Laura Jiménez</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SysAdmin</t>
+          <t>Scrum Master</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1905,17 +3445,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TEC-13</t>
+          <t>TEC-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Natalia Ortiz</t>
+          <t>Marcos López</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DBA (Base de Datos)</t>
+          <t>Arquitecto de Software</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1925,17 +3465,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TEC-14</t>
+          <t>TEC-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Oscar Prieto</t>
+          <t>Natalia Ortiz</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Arquitecto de Software</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1945,21 +3485,161 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TEC-15</t>
+          <t>TEC-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Patricia Rojas</t>
+          <t>Oscar Díaz</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Arquitecto de Software</t>
+          <t>Frontend Developer</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TEC-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Patricia Rojas</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TEC-16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Raúl Mendoza</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TEC-17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sofía Vargas</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SysAdmin</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TEC-18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tomás Fuentes</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Product Owner</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TEC-19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Úrsula Perea</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Arquitecto de Software</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TEC-20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Víctor Reyes</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SysAdmin</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TEC-21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Andrés Pérez </t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Bidding Technician</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -1973,7 +3653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2006,23 +3686,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TEC-02</t>
+          <t>TEC-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Beatriz Gómez</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
+          <t>Ana Martínez</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>46202</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2033,50 +3709,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TEC-03</t>
+          <t>TEC-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Carlos Vega</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
+          <t>Víctor Reyes</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>46230</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vacaciones</t>
+          <t>Baja Médica</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TEC-05</t>
+          <t>TEC-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Elena Navarro</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
+          <t>Laura Jiménez</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46237</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2087,27 +3755,207 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TEC-13</t>
+          <t>TEC-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Natalia Ortiz</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
+          <t>Ana Martínez</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>46222</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46232</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Vacaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TEC-06</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fernando Gil</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>46208</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Baja Médica</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TEC-04</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Diana Torres</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46194</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Vacaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TEC-14</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Oscar Díaz</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Permiso Personal</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TEC-18</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tomás Fuentes</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Baja Médica</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TEC-18</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tomás Fuentes</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Permiso Personal</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TEC-05</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Elena Navarro</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Permiso Personal</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TEC-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Carlos Vega</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Permiso Personal</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TEC-15</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Patricia Rojas</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Baja Médica</t>
         </is>
       </c>
     </row>
